--- a/public/post/drafts/weekly-picks/2025Ruka/fantasy-team.xlsx
+++ b/public/post/drafts/weekly-picks/2025Ruka/fantasy-team.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t xml:space="preserve">Skier</t>
   </si>
@@ -32,42 +32,66 @@
     <t xml:space="preserve">Avg_Volatility</t>
   </si>
   <si>
-    <t xml:space="preserve">Therese Johaug</t>
+    <t xml:space="preserve">Kerttu Niskanen</t>
   </si>
   <si>
     <t xml:space="preserve">f</t>
   </si>
   <si>
+    <t xml:space="preserve">Finland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.433185878821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosie Brennan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.594443085999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ebba Andersson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.109066454503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katharina Hennig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.684564576176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Krista Pärmäkoski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.785697711092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teresa Stadlober</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.56194557913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Astrid Øyre Slind</t>
+  </si>
+  <si>
     <t xml:space="preserve">Norway</t>
   </si>
   <si>
-    <t xml:space="preserve">176.858946138455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kerttu Niskanen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.433185878821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Krista Pärmäkoski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.785697711092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lotta Udnes Weng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.303135332004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Astrid Øyre Slind</t>
-  </si>
-  <si>
     <t xml:space="preserve">114.227956719251</t>
   </si>
   <si>
@@ -77,18 +101,6 @@
     <t xml:space="preserve">135.855584268851</t>
   </si>
   <si>
-    <t xml:space="preserve">Kristin Austgulen Fosnæs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.6383190229012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silje Theodorsen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.961192035993</t>
-  </si>
-  <si>
     <t xml:space="preserve">Johannes Høsflot Klæbo</t>
   </si>
   <si>
@@ -104,12 +116,6 @@
     <t xml:space="preserve">193.963230320742</t>
   </si>
   <si>
-    <t xml:space="preserve">Erik Valnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.931750656113</t>
-  </si>
-  <si>
     <t xml:space="preserve">Iivo Niskanen</t>
   </si>
   <si>
@@ -122,16 +128,28 @@
     <t xml:space="preserve">148.290691217623</t>
   </si>
   <si>
-    <t xml:space="preserve">Simen Hegstad Krüger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.677353184158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lauri Vuorinen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4362556034135</t>
+    <t xml:space="preserve">Federico Pellegrino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.253871515516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mika Vermeulen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.673475883139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antoine Cyr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.960953556265</t>
   </si>
   <si>
     <t xml:space="preserve">Emil Iversen</t>
@@ -497,13 +515,13 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>13214</v>
+        <v>9183</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>10.2148815811242</v>
+        <v>18.9582228138091</v>
       </c>
     </row>
     <row r="3">
@@ -517,13 +535,13 @@
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>9183</v>
+        <v>8390</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>18.9582228138091</v>
+        <v>17.9957267264068</v>
       </c>
     </row>
     <row r="4">
@@ -534,41 +552,41 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>4296</v>
+        <v>7994</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>22.7949646706652</v>
+        <v>17.396026717405</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>3821</v>
+        <v>6309</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
-        <v>21.5846881672482</v>
+        <v>18.8021411130001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -577,58 +595,58 @@
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>3567</v>
+        <v>4296</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>24.0771793984285</v>
+        <v>22.7949646706652</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>2345</v>
+        <v>3572</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F7" t="n">
-        <v>20.0357634843542</v>
+        <v>12.7512579798807</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>1898</v>
+        <v>3567</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F8" t="n">
-        <v>14.6024129147765</v>
+        <v>24.0771793984285</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
@@ -637,30 +655,30 @@
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>2345</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F9" t="n">
-        <v>16.2909290200135</v>
+        <v>20.0357634843542</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
         <v>25</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>15622</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F10" t="n">
         <v>18.4555274504439</v>
@@ -668,19 +686,19 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D11" t="n">
         <v>13062</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F11" t="n">
         <v>20.678303577915</v>
@@ -688,119 +706,119 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
         <v>30</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>10990</v>
+        <v>6307</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F12" t="n">
-        <v>23.2554191839388</v>
+        <v>20.9253504491108</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>6307</v>
+        <v>6266</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F13" t="n">
-        <v>20.9253504491108</v>
+        <v>18.1886318937552</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>6266</v>
+        <v>5882</v>
       </c>
       <c r="E14" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F14" t="n">
-        <v>18.1886318937552</v>
+        <v>23.6151922712191</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>5515</v>
+        <v>3666</v>
       </c>
       <c r="E15" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F15" t="n">
-        <v>29.0986952618389</v>
+        <v>20.5229812226172</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="D16" t="n">
-        <v>2456</v>
+        <v>2783</v>
       </c>
       <c r="E16" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F16" t="n">
-        <v>19.4731142729381</v>
+        <v>19.8652528572775</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D17" t="n">
         <v>610</v>
       </c>
       <c r="E17" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F17" t="n">
         <v>29.8161419140249</v>

--- a/public/post/drafts/weekly-picks/2025Ruka/fantasy-team.xlsx
+++ b/public/post/drafts/weekly-picks/2025Ruka/fantasy-team.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t xml:space="preserve">Skier</t>
   </si>
@@ -32,73 +32,70 @@
     <t xml:space="preserve">Avg_Volatility</t>
   </si>
   <si>
+    <t xml:space="preserve">Jonna Sundling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.5120605298</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kerttu Niskanen</t>
   </si>
   <si>
-    <t xml:space="preserve">f</t>
-  </si>
-  <si>
     <t xml:space="preserve">Finland</t>
   </si>
   <si>
     <t xml:space="preserve">176.433185878821</t>
   </si>
   <si>
-    <t xml:space="preserve">Rosie Brennan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.594443085999</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ebba Andersson</t>
   </si>
   <si>
-    <t xml:space="preserve">Sweden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.109066454503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katharina Hennig</t>
+    <t xml:space="preserve">140.948914097815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Krista Pärmäkoski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.785697711092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teresa Stadlober</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.56194557913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Astrid Øyre Slind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Norway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.227956719251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johanna Matintalo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.855584268851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laura Gimmler</t>
   </si>
   <si>
     <t xml:space="preserve">Germany</t>
   </si>
   <si>
-    <t xml:space="preserve">138.684564576176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Krista Pärmäkoski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.785697711092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teresa Stadlober</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.56194557913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Astrid Øyre Slind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Norway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.227956719251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johanna Matintalo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.855584268851</t>
+    <t xml:space="preserve">89.2220286083683</t>
   </si>
   <si>
     <t xml:space="preserve">Johannes Høsflot Klæbo</t>
@@ -137,10 +134,10 @@
     <t xml:space="preserve">130.253871515516</t>
   </si>
   <si>
-    <t xml:space="preserve">Mika Vermeulen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.673475883139</t>
+    <t xml:space="preserve">Simen Hegstad Krüger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.677353184158</t>
   </si>
   <si>
     <t xml:space="preserve">Antoine Cyr</t>
@@ -515,13 +512,13 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>9183</v>
+        <v>11536</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>18.9582228138091</v>
+        <v>17.995951717078</v>
       </c>
     </row>
     <row r="3">
@@ -535,13 +532,13 @@
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>8390</v>
+        <v>9183</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>17.9957267264068</v>
+        <v>18.9582228138091</v>
       </c>
     </row>
     <row r="4">
@@ -552,13 +549,13 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>7994</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4" t="n">
         <v>17.396026717405</v>
@@ -566,119 +563,119 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>6309</v>
+        <v>4296</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F5" t="n">
-        <v>18.8021411130001</v>
+        <v>22.7949646706652</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>4296</v>
+        <v>3572</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F6" t="n">
-        <v>22.7949646706652</v>
+        <v>12.7512579798807</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
       </c>
       <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3567</v>
+      </c>
+      <c r="E7" t="s">
         <v>22</v>
       </c>
-      <c r="D7" t="n">
-        <v>3572</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
-      </c>
       <c r="F7" t="n">
-        <v>12.7512579798807</v>
+        <v>24.0771793984285</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>3567</v>
+        <v>2345</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F8" t="n">
-        <v>24.0771793984285</v>
+        <v>20.0357634843542</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>2345</v>
+        <v>1441</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F9" t="n">
-        <v>20.0357634843542</v>
+        <v>19.6583849193893</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
         <v>29</v>
       </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D10" t="n">
         <v>15622</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
         <v>18.4555274504439</v>
@@ -686,19 +683,19 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
         <v>13062</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F11" t="n">
         <v>20.678303577915</v>
@@ -706,19 +703,19 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
         <v>6307</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F12" t="n">
         <v>20.9253504491108</v>
@@ -726,19 +723,19 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D13" t="n">
         <v>6266</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13" t="n">
         <v>18.1886318937552</v>
@@ -746,19 +743,19 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
         <v>38</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" t="s">
-        <v>39</v>
       </c>
       <c r="D14" t="n">
         <v>5882</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F14" t="n">
         <v>23.6151922712191</v>
@@ -766,39 +763,39 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5515</v>
+      </c>
+      <c r="E15" t="s">
         <v>41</v>
       </c>
-      <c r="B15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3666</v>
-      </c>
-      <c r="E15" t="s">
-        <v>42</v>
-      </c>
       <c r="F15" t="n">
-        <v>20.5229812226172</v>
+        <v>29.0986952618389</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
         <v>43</v>
-      </c>
-      <c r="B16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" t="s">
-        <v>44</v>
       </c>
       <c r="D16" t="n">
         <v>2783</v>
       </c>
       <c r="E16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F16" t="n">
         <v>19.8652528572775</v>
@@ -806,19 +803,19 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D17" t="n">
         <v>610</v>
       </c>
       <c r="E17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F17" t="n">
         <v>29.8161419140249</v>
